--- a/data/trending_integrated_20260914_12.xlsx
+++ b/data/trending_integrated_20260914_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9740</v>
+        <v>10270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.29%</t>
+          <t>+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -601,7 +601,7 @@
         <v>7790</v>
       </c>
       <c r="L2" t="n">
-        <v>9970</v>
+        <v>10270</v>
       </c>
       <c r="M2" t="n">
         <v>7700</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>236221680415</v>
+        <v>264315411975</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 테마 부각. 급락장 속에서도 긍정적 흐름 유지 전망.</t>
+          <t>차세대 광반도체 및 광통신 테마, 주포와 프로그램 매수세에 따른 급등 기대감. 단기 과열 경계 신호 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '프로그램']</t>
+          <t>['광반도체', '광통신', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6620</v>
+        <v>6550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.15%</t>
+          <t>+18.87%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>48738629555</v>
+        <v>49143723325</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8720</v>
+        <v>4570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.24%</t>
+          <t>+18.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.55</v>
+        <v>-0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>1.25</v>
+        <v>0.59</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7910</v>
+        <v>3870</v>
       </c>
       <c r="K4" t="n">
-        <v>7800</v>
+        <v>3860</v>
       </c>
       <c r="L4" t="n">
-        <v>9840</v>
+        <v>4580</v>
       </c>
       <c r="M4" t="n">
-        <v>7540</v>
+        <v>3740</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="O4" t="n">
-        <v>64593129275</v>
+        <v>162061838096</v>
       </c>
       <c r="P4" t="n">
-        <v>25050</v>
+        <v>8100</v>
       </c>
       <c r="Q4" t="n">
-        <v>3705</v>
+        <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>-24000</v>
+        <v>-217000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['광통신', 'AIDC', '추세적 상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9130</v>
+        <v>9120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.13%</t>
+          <t>+10.01%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
         <v>179</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>31278900885</v>
+        <v>31489407845</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2810</v>
+        <v>2855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>+8.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>91864017213</v>
+        <v>93278470234</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4115</v>
+        <v>8470</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.33%</t>
+          <t>+7.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
         <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.59</v>
+        <v>1.25</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3870</v>
+        <v>7910</v>
       </c>
       <c r="K7" t="n">
-        <v>3860</v>
+        <v>7800</v>
       </c>
       <c r="L7" t="n">
-        <v>4285</v>
+        <v>9840</v>
       </c>
       <c r="M7" t="n">
-        <v>3740</v>
+        <v>7540</v>
       </c>
       <c r="N7" t="n">
-        <v>1.04</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>123901560783</v>
+        <v>65804431225</v>
       </c>
       <c r="P7" t="n">
-        <v>8100</v>
+        <v>25050</v>
       </c>
       <c r="Q7" t="n">
-        <v>592</v>
+        <v>3705</v>
       </c>
       <c r="R7" t="n">
-        <v>-217000</v>
+        <v>-24000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '추세적 상승']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16990</v>
+        <v>16970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>+5.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>246587302330</v>
+        <v>247834064915</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14500</v>
+        <v>14890</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.47%</t>
+          <t>+5.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1245,7 +1245,7 @@
         <v>13850</v>
       </c>
       <c r="L9" t="n">
-        <v>14730</v>
+        <v>14920</v>
       </c>
       <c r="M9" t="n">
         <v>13800</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>97011429315</v>
+        <v>110960683120</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14650</v>
+        <v>14570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-1.97</v>
       </c>
       <c r="E10" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G10" t="n">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="H10" t="n">
         <v>1.17</v>
@@ -1346,7 +1346,7 @@
         <v>3.14</v>
       </c>
       <c r="O10" t="n">
-        <v>99176198490</v>
+        <v>99687134165</v>
       </c>
       <c r="P10" t="n">
         <v>36200</v>
@@ -1391,184 +1391,184 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8250</v>
+        <v>1855</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="E11" t="n">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>839</v>
+        <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>0.75</v>
+        <v>2.08</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8290</v>
+        <v>1878</v>
       </c>
       <c r="K11" t="n">
-        <v>8100</v>
+        <v>1909</v>
       </c>
       <c r="L11" t="n">
-        <v>9050</v>
+        <v>1961</v>
       </c>
       <c r="M11" t="n">
-        <v>8060</v>
+        <v>1840</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>20835519010</v>
+        <v>14748195681</v>
       </c>
       <c r="P11" t="n">
-        <v>21500</v>
+        <v>4795</v>
       </c>
       <c r="Q11" t="n">
-        <v>2300</v>
+        <v>1524</v>
       </c>
       <c r="R11" t="n">
-        <v>64000</v>
+        <v>-224000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>항암 신약 관련 글로벌 심포지엄 개최 및 임상 결과에 대한 기대감으로 인한 목표가 상향 전망.</t>
+          <t>유가 상승 및 중동 불안 심화로 인한 운임 강세 기대에도 불구하고, 해운주 전반의 악재 및 매수세 부진으로 주가 부진. 원가 상승 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['페니트리움바이오', '항암 신약', '임상']</t>
+          <t>['유가', '운임', '중동 불안']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1864</v>
+        <v>8150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.36</v>
+        <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>196</v>
+        <v>871</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1878</v>
+        <v>8290</v>
       </c>
       <c r="K12" t="n">
-        <v>1909</v>
+        <v>8100</v>
       </c>
       <c r="L12" t="n">
-        <v>1961</v>
+        <v>9050</v>
       </c>
       <c r="M12" t="n">
-        <v>1840</v>
+        <v>8060</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>14660708503</v>
+        <v>21599073255</v>
       </c>
       <c r="P12" t="n">
-        <v>4795</v>
+        <v>21500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1524</v>
+        <v>2300</v>
       </c>
       <c r="R12" t="n">
-        <v>-224000</v>
+        <v>64000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>유가 상승 및 중동 불안 심화로 인한 운임 강세 기대에도 불구하고, 해운주 전반의 악재 및 매수세 부진으로 주가 부진. 원가 상승 우려.</t>
+          <t>항암 신약 관련 글로벌 심포지엄 개최 및 임상 결과에 대한 기대감으로 인한 목표가 상향 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['유가', '운임', '중동 불안']</t>
+          <t>['페니트리움바이오', '항암 신약', '임상']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88700</v>
+        <v>88600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F13" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G13" t="n">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="H13" t="n">
         <v>23.56</v>
@@ -1622,7 +1622,7 @@
         <v>23.59</v>
       </c>
       <c r="O13" t="n">
-        <v>142047286600</v>
+        <v>143650541850</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253000</v>
+        <v>252750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.50%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G14" t="n">
-        <v>1686</v>
+        <v>1720</v>
       </c>
       <c r="H14" t="n">
         <v>46.64</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2198024765750</v>
+        <v>2227999680750</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 전망과 함께 주가 하락 우려 제기.</t>
+          <t>정치적 이슈와 현 정권 심판론으로 인한 투자 심리 위축. 반도체 산업 경쟁력 약화 우려. HBM 개발 지연 및 중국 관련 리스크 부각.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['삼성전자', '정치', '주가 하락']</t>
+          <t>['반도체', 'HBM', '이재명']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11900</v>
+        <v>11865</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.72</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" t="n">
         <v>0.22</v>
@@ -1806,7 +1806,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>53677345025</v>
+        <v>54055320295</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1731000</v>
+        <v>1729000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.47%</t>
+          <t>-4.58%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G16" t="n">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="H16" t="n">
         <v>50.47</v>
@@ -1898,7 +1898,7 @@
         <v>50.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3744969081500</v>
+        <v>3789831353500</v>
       </c>
       <c r="P16" t="n">
         <v>2987000</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금리 인상 불확실성 해소 기대로 오후 반등 가능성 언급. 다만, 하락 추세에 대한 우려도 공존.</t>
+          <t>금리 인상 불확실성 해소에 따른 반등 기대감 존재하나, 정부 정책 및 투자자 심리 위축으로 인한 하락세 지속 우려. HBM 경쟁력 및 외인 매매 동향 중요.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['금리인상', '선물매수', 'AI']</t>
+          <t>['금리인상', 'HBM', '외인']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18960</v>
+        <v>18900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="H17" t="n">
         <v>10.55</v>
@@ -1990,7 +1990,7 @@
         <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>51089228115</v>
+        <v>52645332265</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11840</v>
+        <v>13850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.90%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="H18" t="n">
-        <v>17.58</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>12450</v>
+        <v>14710</v>
       </c>
       <c r="K18" t="n">
-        <v>11960</v>
+        <v>14710</v>
       </c>
       <c r="L18" t="n">
-        <v>13900</v>
+        <v>15420</v>
       </c>
       <c r="M18" t="n">
-        <v>11800</v>
+        <v>13700</v>
       </c>
       <c r="N18" t="n">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>55522397605</v>
+        <v>25526147020</v>
       </c>
       <c r="P18" t="n">
-        <v>14350</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>465</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-51000</v>
+        <v>-67000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
+          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
+          <t>['재건축', '부동산 침체', '외인 매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13960</v>
+        <v>11620</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.10%</t>
+          <t>-6.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>217</v>
+        <v>141</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>17.58</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14710</v>
+        <v>12450</v>
       </c>
       <c r="K19" t="n">
-        <v>14710</v>
+        <v>11960</v>
       </c>
       <c r="L19" t="n">
-        <v>15420</v>
+        <v>13900</v>
       </c>
       <c r="M19" t="n">
-        <v>13700</v>
+        <v>11580</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>17.07</v>
       </c>
       <c r="O19" t="n">
-        <v>25134177610</v>
+        <v>56864410430</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>14350</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>465</v>
       </c>
       <c r="R19" t="n">
-        <v>-67000</v>
+        <v>-51000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
+          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['재건축', '부동산 침체', '외인 매도']</t>
+          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>001210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260914_12.xlsx
+++ b/data/trending_integrated_20260914_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>264315411975</v>
+        <v>266090653365</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 테마, 주포와 프로그램 매수세에 따른 급등 기대감. 단기 과열 경계 신호 존재.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 부각되며 3연상 가능성 언급. 일본 코덴시 자회사와의 연관성 및 상한가 잔량에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '주포']</t>
+          <t>['광반도체', '광통신', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6550</v>
+        <v>6610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+18.87%</t>
+          <t>+19.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>49143723325</v>
+        <v>49528246660</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4570</v>
+        <v>4590</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.09%</t>
+          <t>+18.60%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="H4" t="n">
         <v>0.59</v>
@@ -785,7 +785,7 @@
         <v>3860</v>
       </c>
       <c r="L4" t="n">
-        <v>4580</v>
+        <v>4620</v>
       </c>
       <c r="M4" t="n">
         <v>3740</v>
@@ -794,7 +794,7 @@
         <v>1.04</v>
       </c>
       <c r="O4" t="n">
-        <v>162061838096</v>
+        <v>196285548223</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
+          <t>6G 시대 및 AIDC 광통신 기술 성장성 부각. 국책사업 선정 가능성 및 광전자와의 연관성으로 인한 기대감 상승.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '추세적 상승']</t>
+          <t>['6G', '광통신', '국책사업']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9120</v>
+        <v>9190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.01%</t>
+          <t>+10.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H5" t="n">
         <v>0.83</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>31489407845</v>
+        <v>31852900715</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2855</v>
+        <v>2845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.97%</t>
+          <t>+8.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H6" t="n">
         <v>1.44</v>
@@ -978,7 +978,7 @@
         <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>93278470234</v>
+        <v>94149587531</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8470</v>
+        <v>8550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.08%</t>
+          <t>+8.09%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.55</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
         <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>65804431225</v>
+        <v>66402100915</v>
       </c>
       <c r="P7" t="n">
         <v>25050</v>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16970</v>
+        <v>17080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.67%</t>
+          <t>+6.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
         <v>165</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>247834064915</v>
+        <v>249044287720</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14890</v>
+        <v>14870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.23%</t>
+          <t>+5.09%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G9" t="n">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1245,7 +1245,7 @@
         <v>13850</v>
       </c>
       <c r="L9" t="n">
-        <v>14920</v>
+        <v>14950</v>
       </c>
       <c r="M9" t="n">
         <v>13800</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>110960683120</v>
+        <v>125979596195</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14570</v>
+        <v>14700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-1.97</v>
       </c>
       <c r="E10" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F10" t="n">
         <v>146</v>
       </c>
       <c r="G10" t="n">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="H10" t="n">
         <v>1.17</v>
@@ -1346,7 +1346,7 @@
         <v>3.14</v>
       </c>
       <c r="O10" t="n">
-        <v>99687134165</v>
+        <v>100334906890</v>
       </c>
       <c r="P10" t="n">
         <v>36200</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H11" t="n">
         <v>2.08</v>
@@ -1438,7 +1438,7 @@
         <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>14748195681</v>
+        <v>14844875839</v>
       </c>
       <c r="P11" t="n">
         <v>4795</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8150</v>
+        <v>8180</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="H12" t="n">
         <v>0.75</v>
@@ -1530,7 +1530,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>21599073255</v>
+        <v>22161064960</v>
       </c>
       <c r="P12" t="n">
         <v>21500</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88600</v>
+        <v>88400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>191</v>
       </c>
       <c r="F13" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G13" t="n">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="H13" t="n">
         <v>23.56</v>
@@ -1622,7 +1622,7 @@
         <v>23.59</v>
       </c>
       <c r="O13" t="n">
-        <v>143650541850</v>
+        <v>145322095000</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252750</v>
+        <v>252000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G14" t="n">
-        <v>1720</v>
+        <v>1727</v>
       </c>
       <c r="H14" t="n">
         <v>46.64</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2227999680750</v>
+        <v>2281242357000</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 현 정권 심판론으로 인한 투자 심리 위축. 반도체 산업 경쟁력 약화 우려. HBM 개발 지연 및 중국 관련 리스크 부각.</t>
+          <t>정치적 이슈와 맞물려 반등 기대감 및 실망감이 혼재. AI 반도체 경쟁력 및 국장 투자 환경에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', 'HBM', '이재명']</t>
+          <t>['AI', '반도체', '국내주식']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11865</v>
+        <v>11810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.72</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
         <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" t="n">
         <v>0.22</v>
@@ -1800,13 +1800,13 @@
         <v>13230</v>
       </c>
       <c r="M15" t="n">
-        <v>11820</v>
+        <v>11800</v>
       </c>
       <c r="N15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>54055320295</v>
+        <v>54632246225</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1729000</v>
+        <v>1723000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G16" t="n">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H16" t="n">
         <v>50.47</v>
@@ -1898,7 +1898,7 @@
         <v>50.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3789831353500</v>
+        <v>3859303437500</v>
       </c>
       <c r="P16" t="n">
         <v>2987000</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금리 인상 불확실성 해소에 따른 반등 기대감 존재하나, 정부 정책 및 투자자 심리 위축으로 인한 하락세 지속 우려. HBM 경쟁력 및 외인 매매 동향 중요.</t>
+          <t>금리 인상 불확실성 해소에 따른 반등 기대와 동시에 하락 가능성 언급. 외인 선물 매수 전환 여부 및 투자 심리 변동에 대한 관찰.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['금리인상', 'HBM', '외인']</t>
+          <t>['금리인상', '외인선물', '반등']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18900</v>
+        <v>18850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H17" t="n">
         <v>10.55</v>
@@ -1990,7 +1990,7 @@
         <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>52645332265</v>
+        <v>53703082780</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13850</v>
+        <v>13880</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.85%</t>
+          <t>-5.64%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>25526147020</v>
+        <v>26012297575</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11620</v>
+        <v>11590</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.67%</t>
+          <t>-6.91%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.51</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
         <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H19" t="n">
         <v>17.58</v>
@@ -2168,13 +2168,13 @@
         <v>13900</v>
       </c>
       <c r="M19" t="n">
-        <v>11580</v>
+        <v>11510</v>
       </c>
       <c r="N19" t="n">
         <v>17.07</v>
       </c>
       <c r="O19" t="n">
-        <v>56864410430</v>
+        <v>58250382760</v>
       </c>
       <c r="P19" t="n">
         <v>14350</v>

--- a/data/trending_integrated_20260914_12.xlsx
+++ b/data/trending_integrated_20260914_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>266090653365</v>
+        <v>267077620905</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 부각되며 3연상 가능성 언급. 일본 코덴시 자회사와의 연관성 및 상한가 잔량에 대한 기대감 표출.</t>
+          <t>차세대 광반도체 및 광통신 테마로 3연상 기대감. 일본 코덴시 자회사 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '상한가']</t>
+          <t>['광반도체', '광통신', '3연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6610</v>
+        <v>6580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+19.96%</t>
+          <t>+19.42%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>98</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>49528246660</v>
+        <v>49867688390</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4590</v>
+        <v>4505</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.60%</t>
+          <t>+16.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H4" t="n">
         <v>0.59</v>
@@ -794,7 +794,7 @@
         <v>1.04</v>
       </c>
       <c r="O4" t="n">
-        <v>196285548223</v>
+        <v>211562847246</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6G 시대 및 AIDC 광통신 기술 성장성 부각. 국책사업 선정 가능성 및 광전자와의 연관성으로 인한 기대감 상승.</t>
+          <t>6G 시대 도래 및 AIDC 광통신 기술 관련 뉴스 언급. 투자 경고 종목.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['6G', '광통신', '국책사업']</t>
+          <t>['6G', '광통신', 'AIDC']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9190</v>
+        <v>9290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.86%</t>
+          <t>+12.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H5" t="n">
         <v>0.83</v>
@@ -877,7 +877,7 @@
         <v>8300</v>
       </c>
       <c r="L5" t="n">
-        <v>9425</v>
+        <v>9440</v>
       </c>
       <c r="M5" t="n">
         <v>8300</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>31852900715</v>
+        <v>37172751020</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2845</v>
+        <v>2840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.59%</t>
+          <t>+8.40%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
         <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H6" t="n">
         <v>1.44</v>
@@ -978,7 +978,7 @@
         <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>94149587531</v>
+        <v>95583782718</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8550</v>
+        <v>8500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.09%</t>
+          <t>+7.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.55</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
         <v>79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>66402100915</v>
+        <v>66782649355</v>
       </c>
       <c r="P7" t="n">
         <v>25050</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17080</v>
+        <v>17090</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.35%</t>
+          <t>+6.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>249044287720</v>
+        <v>250796693655</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론으로 인한 등락 속에 지지선 이탈 및 반등 시도 관측.</t>
+          <t>AI 개발 속도 조절론에 따른 영향 분석과 함께 주가 상승 기대감. 개인 투자자 매물대 정리.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['엑스게이트', 'AI', '속도 조절론']</t>
+          <t>['AI', '속도조절론', '매물대']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14870</v>
+        <v>14780</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.09%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F9" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>125979596195</v>
+        <v>131661810415</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 관련 AIDC 광통신 기술 성장 수혜 기대. GPU 확보 뉴스와 함께 기술력 부각.</t>
+          <t>AIDC 광통신 기술 관련 뉴스 및 15,000원 돌파 기대감. 광전자 대비 상대적 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['광통신', 'AIDC', '기술력']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14700</v>
+        <v>21900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.97</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>258</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>668</v>
+        <v>174</v>
       </c>
       <c r="H10" t="n">
-        <v>1.17</v>
+        <v>28.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14610</v>
+        <v>21400</v>
       </c>
       <c r="K10" t="n">
-        <v>15420</v>
+        <v>21100</v>
       </c>
       <c r="L10" t="n">
-        <v>16510</v>
+        <v>21900</v>
       </c>
       <c r="M10" t="n">
-        <v>14320</v>
+        <v>20850</v>
       </c>
       <c r="N10" t="n">
-        <v>3.14</v>
+        <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>100334906890</v>
+        <v>34997522750</v>
       </c>
       <c r="P10" t="n">
-        <v>36200</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>8920</v>
+        <v>18440</v>
       </c>
       <c r="R10" t="n">
-        <v>-128000</v>
+        <v>86000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이란-걸프국가 회담 연기 및 호르무즈 해협 긴장 고조로 국제 유가 폭등. 저가 매수 기회 포착.</t>
+          <t>LNG·원유운반선 6척 수주(1.6조원) 및 ISDS 승소 확정. 배당 및 자사주 소각 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['수주', 'LNG', 'ISDS']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1856</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+1.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.36</v>
+        <v>-0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="G11" t="n">
-        <v>204</v>
+        <v>905</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>0.75</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1878</v>
+        <v>8290</v>
       </c>
       <c r="K11" t="n">
-        <v>1909</v>
+        <v>8100</v>
       </c>
       <c r="L11" t="n">
-        <v>1961</v>
+        <v>9050</v>
       </c>
       <c r="M11" t="n">
-        <v>1840</v>
+        <v>8060</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>14844875839</v>
+        <v>22660352740</v>
       </c>
       <c r="P11" t="n">
-        <v>4795</v>
+        <v>21500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1524</v>
+        <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>-224000</v>
+        <v>64000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>유가 상승 및 중동 불안 심화로 인한 운임 강세 기대에도 불구하고, 해운주 전반의 악재 및 매수세 부진으로 주가 부진. 원가 상승 우려.</t>
+          <t>암 치료 바이오 신약 개발 및 글로벌 심포지엄 개최. 임상 결과 기대감으로 목표가 30만원 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['유가', '운임', '중동 불안']</t>
+          <t>['바이오신약', '항암', '임상']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8180</v>
+        <v>14770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+1.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.54</v>
+        <v>-1.97</v>
       </c>
       <c r="E12" t="n">
-        <v>160</v>
+        <v>262</v>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="G12" t="n">
-        <v>891</v>
+        <v>673</v>
       </c>
       <c r="H12" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8290</v>
+        <v>14610</v>
       </c>
       <c r="K12" t="n">
-        <v>8100</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>9050</v>
+        <v>16510</v>
       </c>
       <c r="M12" t="n">
-        <v>8060</v>
+        <v>14320</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="O12" t="n">
-        <v>22161064960</v>
+        <v>101614931110</v>
       </c>
       <c r="P12" t="n">
-        <v>21500</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>64000</v>
+        <v>-128000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>항암 신약 관련 글로벌 심포지엄 개최 및 임상 결과에 대한 기대감으로 인한 목표가 상향 전망.</t>
+          <t>이란-걸프국가 회담 연기 및 호르무즈 해협 긴장 고조로 국제 유가 폭등. 저가 매수 기회 포착.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['페니트리움바이오', '항암 신약', '임상']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88400</v>
+        <v>1858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.03</v>
+        <v>-0.36</v>
       </c>
       <c r="E13" t="n">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>656</v>
+        <v>209</v>
       </c>
       <c r="H13" t="n">
-        <v>23.56</v>
+        <v>2.08</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>90800</v>
+        <v>1878</v>
       </c>
       <c r="K13" t="n">
-        <v>89800</v>
+        <v>1909</v>
       </c>
       <c r="L13" t="n">
-        <v>90400</v>
+        <v>1961</v>
       </c>
       <c r="M13" t="n">
-        <v>87700</v>
+        <v>1840</v>
       </c>
       <c r="N13" t="n">
-        <v>23.59</v>
+        <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>145322095000</v>
+        <v>14933899607</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>4795</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>1524</v>
       </c>
       <c r="R13" t="n">
-        <v>-464000</v>
+        <v>-224000</v>
       </c>
       <c r="S13" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국제 유가 상승 수혜 기대감 속 원전주 상승 가능성 언급. 공매도 세력과의 차익 실현 공방 예상.</t>
+          <t>유가 상승 및 중동 불안 심화로 인한 운임 강세 기대에도 불구하고, 해운주 전반의 악재 및 매수세 부진으로 주가 부진. 원가 상승 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국제유가', '원전주', '공매도']</t>
+          <t>['유가', '운임', '중동 불안']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252000</v>
+        <v>88300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>195</v>
       </c>
       <c r="F14" t="n">
-        <v>494</v>
+        <v>112</v>
       </c>
       <c r="G14" t="n">
-        <v>1727</v>
+        <v>668</v>
       </c>
       <c r="H14" t="n">
-        <v>46.64</v>
+        <v>23.56</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>259500</v>
+        <v>90800</v>
       </c>
       <c r="K14" t="n">
-        <v>249500</v>
+        <v>89800</v>
       </c>
       <c r="L14" t="n">
-        <v>254500</v>
+        <v>90400</v>
       </c>
       <c r="M14" t="n">
-        <v>249000</v>
+        <v>87700</v>
       </c>
       <c r="N14" t="n">
-        <v>46.71</v>
+        <v>23.59</v>
       </c>
       <c r="O14" t="n">
-        <v>2281242357000</v>
+        <v>146529226100</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>75900</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-2179000</v>
+        <v>-464000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1014000</v>
+        <v>-70000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 반등 기대감 및 실망감이 혼재. AI 반도체 경쟁력 및 국장 투자 환경에 대한 부정적 전망.</t>
+          <t>국제 유가 상승 수혜 기대감 속 원전주 상승 가능성 언급. 공매도 세력과의 차익 실현 공방 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '국내주식']</t>
+          <t>['국제유가', '원전주', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11810</v>
+        <v>252250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.72</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>492</v>
       </c>
       <c r="G15" t="n">
-        <v>61</v>
+        <v>1719</v>
       </c>
       <c r="H15" t="n">
-        <v>0.22</v>
+        <v>46.64</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12290</v>
+        <v>259500</v>
       </c>
       <c r="K15" t="n">
-        <v>12030</v>
+        <v>249500</v>
       </c>
       <c r="L15" t="n">
-        <v>13230</v>
+        <v>254500</v>
       </c>
       <c r="M15" t="n">
-        <v>11800</v>
+        <v>249000</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9399999999999999</v>
+        <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>54632246225</v>
+        <v>2332254621500</v>
       </c>
       <c r="P15" t="n">
-        <v>20850</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>4020</v>
+        <v>75900</v>
       </c>
       <c r="R15" t="n">
-        <v>2000</v>
+        <v>-2179000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-1014000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
+          <t>정치적 이슈와 AI 속도 조절론 등 거시 경제 불확실성에 따른 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,143 +1831,143 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '재료 소멸']</t>
+          <t>['AI', '정치', '경제']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1723000</v>
+        <v>11800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.08</v>
+        <v>-0.72</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>514</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>1223</v>
+        <v>62</v>
       </c>
       <c r="H16" t="n">
-        <v>50.47</v>
+        <v>0.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1812000</v>
+        <v>12290</v>
       </c>
       <c r="K16" t="n">
-        <v>1707000</v>
+        <v>12030</v>
       </c>
       <c r="L16" t="n">
-        <v>1740000</v>
+        <v>13230</v>
       </c>
       <c r="M16" t="n">
-        <v>1695000</v>
+        <v>11770</v>
       </c>
       <c r="N16" t="n">
-        <v>50.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>3859303437500</v>
+        <v>55198525795</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>20850</v>
       </c>
       <c r="Q16" t="n">
-        <v>325000</v>
+        <v>4020</v>
       </c>
       <c r="R16" t="n">
-        <v>-897000</v>
+        <v>2000</v>
       </c>
       <c r="S16" t="n">
-        <v>-147000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금리 인상 불확실성 해소에 따른 반등 기대와 동시에 하락 가능성 언급. 외인 선물 매수 전환 여부 및 투자 심리 변동에 대한 관찰.</t>
+          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['금리인상', '외인선물', '반등']</t>
+          <t>['원전주', '폭락', '재료 소멸']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18850</v>
+        <v>1723000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>520</v>
       </c>
       <c r="G17" t="n">
-        <v>316</v>
+        <v>1287</v>
       </c>
       <c r="H17" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K17" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L17" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M17" t="n">
-        <v>18780</v>
+        <v>1695000</v>
       </c>
       <c r="N17" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O17" t="n">
-        <v>53703082780</v>
+        <v>3915599513500</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R17" t="n">
-        <v>-430000</v>
+        <v>-897000</v>
       </c>
       <c r="S17" t="n">
-        <v>-48000</v>
+        <v>-147000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
+          <t>금리 인상 불확실성 해소 기대감과 함께 하락 후 반등 가능성 언급. 개미 투자자 비관론.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '반등 기대']</t>
+          <t>['금리인상', '반등', '투자']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13880</v>
+        <v>18880</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.64%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>236</v>
+        <v>330</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>10.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14710</v>
+        <v>19890</v>
       </c>
       <c r="K18" t="n">
-        <v>14710</v>
+        <v>19480</v>
       </c>
       <c r="L18" t="n">
-        <v>15420</v>
+        <v>19550</v>
       </c>
       <c r="M18" t="n">
-        <v>13700</v>
+        <v>18780</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>10.65</v>
       </c>
       <c r="O18" t="n">
-        <v>26012297575</v>
+        <v>54837810605</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-67000</v>
+        <v>-430000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
+          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['재건축', '부동산 침체', '외인 매도']</t>
+          <t>['대차 해지', '공매도', '반등 기대']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11590</v>
+        <v>13860</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.91%</t>
+          <t>-5.78%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="H19" t="n">
-        <v>17.58</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12450</v>
+        <v>14710</v>
       </c>
       <c r="K19" t="n">
-        <v>11960</v>
+        <v>14710</v>
       </c>
       <c r="L19" t="n">
-        <v>13900</v>
+        <v>15420</v>
       </c>
       <c r="M19" t="n">
-        <v>11510</v>
+        <v>13700</v>
       </c>
       <c r="N19" t="n">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>58250382760</v>
+        <v>26396503680</v>
       </c>
       <c r="P19" t="n">
-        <v>14350</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>465</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-51000</v>
+        <v>-67000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
+          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,18 +2199,110 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>['재건축', '부동산 침체', '외인 매도']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>금호전기</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11560</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-7.15%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" t="n">
+        <v>154</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>12450</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11960</v>
+      </c>
+      <c r="L20" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11510</v>
+      </c>
+      <c r="N20" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="O20" t="n">
+        <v>58831085510</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14350</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>465</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
         </is>
       </c>
-      <c r="X19" t="n">
+      <c r="X20" t="n">
         <v>1</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>추적</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>001210</t>
         </is>

--- a/data/trending_integrated_20260914_12.xlsx
+++ b/data/trending_integrated_20260914_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>267077620905</v>
+        <v>267781978585</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6580</v>
+        <v>6520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+19.42%</t>
+          <t>+18.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>49867688390</v>
+        <v>50186646305</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4505</v>
+        <v>4545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+16.41%</t>
+          <t>+17.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H4" t="n">
         <v>0.59</v>
@@ -794,7 +794,7 @@
         <v>1.04</v>
       </c>
       <c r="O4" t="n">
-        <v>211562847246</v>
+        <v>225613927216</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6G 시대 도래 및 AIDC 광통신 기술 관련 뉴스 언급. 투자 경고 종목.</t>
+          <t>6G, AIDC, 광통신 관련 기술 개발 및 국책 사업 선정 가능성 등 구체적인 성장 동력 언급. 주가 상승에 대한 기대감 고조.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['6G', '광통신', 'AIDC']</t>
+          <t>['광통신', 'AI', '국책사업']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9290</v>
+        <v>9230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+12.06%</t>
+          <t>+11.34%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H5" t="n">
         <v>0.83</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>37172751020</v>
+        <v>38142559135</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2840</v>
+        <v>2810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.40%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H6" t="n">
         <v>1.44</v>
@@ -978,7 +978,7 @@
         <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>95583782718</v>
+        <v>96132508962</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8500</v>
+        <v>8380</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.46%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>66782649355</v>
+        <v>67404513285</v>
       </c>
       <c r="P7" t="n">
         <v>25050</v>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17090</v>
+        <v>17010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.41%</t>
+          <t>+5.92%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
         <v>169</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>250796693655</v>
+        <v>251686857120</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14780</v>
+        <v>14910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>+5.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>131661810415</v>
+        <v>138968718810</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 관련 뉴스 및 15,000원 돌파 기대감. 광전자 대비 상대적 상승 기대.</t>
+          <t>GPU, AI 등 성장 산업 관련 광통신 기술력 부각 및 대규모 수주 기대감. 15,000원 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '기술력']</t>
+          <t>['광통신', 'AI', '수주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>34997522750</v>
+        <v>36238553750</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LNG·원유운반선 6척 수주(1.6조원) 및 ISDS 승소 확정. 배당 및 자사주 소각 기대감.</t>
+          <t>대규모 수주 공시 및 ISDS 승소 확정 등 구체적인 팩트 기반 호재 확인. 배당 및 자사주 소각 기대감도 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', 'LNG', 'ISDS']</t>
+          <t>['수주', '공시', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>14920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.69%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.54</v>
+        <v>-1.97</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="G11" t="n">
-        <v>905</v>
+        <v>690</v>
       </c>
       <c r="H11" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8290</v>
+        <v>14610</v>
       </c>
       <c r="K11" t="n">
-        <v>8100</v>
+        <v>15420</v>
       </c>
       <c r="L11" t="n">
-        <v>9050</v>
+        <v>16510</v>
       </c>
       <c r="M11" t="n">
-        <v>8060</v>
+        <v>14320</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="O11" t="n">
-        <v>22660352740</v>
+        <v>103138952090</v>
       </c>
       <c r="P11" t="n">
-        <v>21500</v>
+        <v>36200</v>
       </c>
       <c r="Q11" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R11" t="n">
-        <v>64000</v>
+        <v>-128000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>암 치료 바이오 신약 개발 및 글로벌 심포지엄 개최. 임상 결과 기대감으로 목표가 30만원 언급.</t>
+          <t>이란-걸프국가 회담 연기 및 호르무즈 해협 긴장 고조로 국제 유가 폭등. 저가 매수 기회 포착.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['바이오신약', '항암', '임상']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14770</v>
+        <v>8260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.10%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.97</v>
+        <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>262</v>
+        <v>168</v>
       </c>
       <c r="F12" t="n">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="G12" t="n">
-        <v>673</v>
+        <v>950</v>
       </c>
       <c r="H12" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14610</v>
+        <v>8290</v>
       </c>
       <c r="K12" t="n">
-        <v>15420</v>
+        <v>8100</v>
       </c>
       <c r="L12" t="n">
-        <v>16510</v>
+        <v>9050</v>
       </c>
       <c r="M12" t="n">
-        <v>14320</v>
+        <v>8060</v>
       </c>
       <c r="N12" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>101614931110</v>
+        <v>23088323025</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>21500</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R12" t="n">
-        <v>-128000</v>
+        <v>64000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>이란-걸프국가 회담 연기 및 호르무즈 해협 긴장 고조로 국제 유가 폭등. 저가 매수 기회 포착.</t>
+          <t>글로벌 제약사 멘토링 및 항암 신약 관련 심포지엄 개최 등 구체적인 재료와 함께 임상 결과에 대한 기대감 높음. 시총 대비 높은 목표가 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['신약', '임상', '항암']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1858</v>
+        <v>1867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.36</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H13" t="n">
         <v>2.08</v>
@@ -1622,7 +1622,7 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>14933899607</v>
+        <v>15100738224</v>
       </c>
       <c r="P13" t="n">
         <v>4795</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88300</v>
+        <v>88200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F14" t="n">
         <v>112</v>
       </c>
       <c r="G14" t="n">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="H14" t="n">
         <v>23.56</v>
@@ -1714,7 +1714,7 @@
         <v>23.59</v>
       </c>
       <c r="O14" t="n">
-        <v>146529226100</v>
+        <v>148577809950</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>252250</v>
+        <v>252000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G15" t="n">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>2332254621500</v>
+        <v>2365784350250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈와 AI 속도 조절론 등 거시 경제 불확실성에 따른 부정적 전망.</t>
+          <t>정치적 언급 위주로, 실제 사업이나 실적에 대한 구체적인 팩트 기반 분석은 부족한 상황.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '정치', '경제']</t>
+          <t>['정치', '투자', '전망']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11800</v>
+        <v>11810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.99%</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.72</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H16" t="n">
         <v>0.22</v>
@@ -1892,13 +1892,13 @@
         <v>13230</v>
       </c>
       <c r="M16" t="n">
-        <v>11770</v>
+        <v>11760</v>
       </c>
       <c r="N16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>55198525795</v>
+        <v>55443838975</v>
       </c>
       <c r="P16" t="n">
         <v>20850</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1723000</v>
+        <v>18870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>520</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>1287</v>
+        <v>338</v>
       </c>
       <c r="H17" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K17" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L17" t="n">
-        <v>1740000</v>
+        <v>19550</v>
       </c>
       <c r="M17" t="n">
-        <v>1695000</v>
+        <v>18780</v>
       </c>
       <c r="N17" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>3915599513500</v>
+        <v>55770216885</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-897000</v>
+        <v>-430000</v>
       </c>
       <c r="S17" t="n">
-        <v>-147000</v>
+        <v>-48000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>금리 인상 불확실성 해소 기대감과 함께 하락 후 반등 가능성 언급. 개미 투자자 비관론.</t>
+          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['금리인상', '반등', '투자']</t>
+          <t>['대차 해지', '공매도', '반등 기대']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18880</v>
+        <v>1718000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.08%</t>
+          <t>-5.19%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>509</v>
       </c>
       <c r="G18" t="n">
-        <v>330</v>
+        <v>1340</v>
       </c>
       <c r="H18" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,60 +2067,60 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K18" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L18" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M18" t="n">
-        <v>18780</v>
+        <v>1695000</v>
       </c>
       <c r="N18" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>54837810605</v>
+        <v>3982490875500</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R18" t="n">
-        <v>-430000</v>
+        <v>-897000</v>
       </c>
       <c r="S18" t="n">
-        <v>-48000</v>
+        <v>-147000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
+          <t>금리 인상 불확실성 해소 기대감과 함께 주가 하락에 대한 우려가 혼재. 투자자들의 심리적 동요가 큰 상태.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '반등 기대']</t>
+          <t>['금리', '주가', '심리']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13860</v>
+        <v>13870</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.78%</t>
+          <t>-5.71%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>26396503680</v>
+        <v>26679955930</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11560</v>
+        <v>11540</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.15%</t>
+          <t>-7.31%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.51</v>
       </c>
       <c r="E20" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H20" t="n">
         <v>17.58</v>
@@ -2260,13 +2260,13 @@
         <v>13900</v>
       </c>
       <c r="M20" t="n">
-        <v>11510</v>
+        <v>11430</v>
       </c>
       <c r="N20" t="n">
         <v>17.07</v>
       </c>
       <c r="O20" t="n">
-        <v>58831085510</v>
+        <v>59858135050</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
+          <t>외인 매수세 유입과 거래량 증가에 따른 단기 급등 기대감, 그러나 투자 주의 및 외인 매도 전환 가능성 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
+          <t>['수급', '거래량', '단기']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">

--- a/data/trending_integrated_20260914_12.xlsx
+++ b/data/trending_integrated_20260914_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>267781978585</v>
+        <v>268170451605</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6520</v>
+        <v>6410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+18.33%</t>
+          <t>+16.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>50186646305</v>
+        <v>51196837460</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4545</v>
+        <v>4460</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+17.44%</t>
+          <t>+15.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
         <v>0.59</v>
@@ -794,7 +794,7 @@
         <v>1.04</v>
       </c>
       <c r="O4" t="n">
-        <v>225613927216</v>
+        <v>234849803449</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6G, AIDC, 광통신 관련 기술 개발 및 국책 사업 선정 가능성 등 구체적인 성장 동력 언급. 주가 상승에 대한 기대감 고조.</t>
+          <t>6G 시대 개막과 광통신 기술 발전에 따른 급등 기대감. 국책사업 선정 및 기술 개발 뉴스 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '국책사업']</t>
+          <t>['6G', '광통신', '국책사업']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9230</v>
+        <v>9270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.34%</t>
+          <t>+11.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H5" t="n">
         <v>0.83</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>38142559135</v>
+        <v>38485622195</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2810</v>
+        <v>2825</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>+7.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H6" t="n">
         <v>1.44</v>
@@ -978,7 +978,7 @@
         <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>96132508962</v>
+        <v>96980659704</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8380</v>
+        <v>17070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.94%</t>
+          <t>+6.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="H7" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7910</v>
+        <v>16060</v>
       </c>
       <c r="K7" t="n">
-        <v>7800</v>
+        <v>16780</v>
       </c>
       <c r="L7" t="n">
-        <v>9840</v>
+        <v>18610</v>
       </c>
       <c r="M7" t="n">
-        <v>7540</v>
+        <v>16230</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>2.39</v>
       </c>
       <c r="O7" t="n">
-        <v>67404513285</v>
+        <v>252356427515</v>
       </c>
       <c r="P7" t="n">
-        <v>25050</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>3705</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-24000</v>
+        <v>-292000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>AI 개발 속도 조절론에 따른 영향 분석과 함께 주가 상승 기대감. 개인 투자자 매물대 정리.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['AI', '속도조절론', '매물대']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17010</v>
+        <v>8380</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.92%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.31</v>
+        <v>0.55</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16060</v>
+        <v>7910</v>
       </c>
       <c r="K8" t="n">
-        <v>16780</v>
+        <v>7800</v>
       </c>
       <c r="L8" t="n">
-        <v>18610</v>
+        <v>9840</v>
       </c>
       <c r="M8" t="n">
-        <v>16230</v>
+        <v>7540</v>
       </c>
       <c r="N8" t="n">
-        <v>2.39</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>251686857120</v>
+        <v>67815911915</v>
       </c>
       <c r="P8" t="n">
-        <v>30550</v>
+        <v>25050</v>
       </c>
       <c r="Q8" t="n">
-        <v>6100</v>
+        <v>3705</v>
       </c>
       <c r="R8" t="n">
-        <v>-292000</v>
+        <v>-24000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 따른 영향 분석과 함께 주가 상승 기대감. 개인 투자자 매물대 정리.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '속도조절론', '매물대']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14910</v>
+        <v>14760</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.37%</t>
+          <t>+4.31%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>138968718810</v>
+        <v>142986517670</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21900</v>
+        <v>21950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+2.57%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1337,7 +1337,7 @@
         <v>21100</v>
       </c>
       <c r="L10" t="n">
-        <v>21900</v>
+        <v>21950</v>
       </c>
       <c r="M10" t="n">
         <v>20850</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>36238553750</v>
+        <v>39045567250</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대규모 수주 공시 및 ISDS 승소 확정 등 구체적인 팩트 기반 호재 확인. 배당 및 자사주 소각 기대감도 존재.</t>
+          <t>LNG·원유운반선 총 6척 수주 성공. 1.6조원 규모의 대규모 수주 공시 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '공시', '실적']</t>
+          <t>['수주', 'LNG선', '원유운반선']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14920</v>
+        <v>14800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-1.97</v>
       </c>
       <c r="E11" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G11" t="n">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="H11" t="n">
         <v>1.17</v>
@@ -1438,7 +1438,7 @@
         <v>3.14</v>
       </c>
       <c r="O11" t="n">
-        <v>103138952090</v>
+        <v>104155067920</v>
       </c>
       <c r="P11" t="n">
         <v>36200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이란-걸프국가 회담 연기 및 호르무즈 해협 긴장 고조로 국제 유가 폭등. 저가 매수 기회 포착.</t>
+          <t>국제 유가 폭등 및 지정학적 리스크 부각. 호르무즈 해협 관련 회담 연기 및 폭발음 소식에 따른 변동성 확대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['국제유가', '호르무즈', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8260</v>
+        <v>8350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G12" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="H12" t="n">
         <v>0.75</v>
@@ -1530,7 +1530,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>23088323025</v>
+        <v>23282993405</v>
       </c>
       <c r="P12" t="n">
         <v>21500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>글로벌 제약사 멘토링 및 항암 신약 관련 심포지엄 개최 등 구체적인 재료와 함께 임상 결과에 대한 기대감 높음. 시총 대비 높은 목표가 제시.</t>
+          <t>항암 신약 관련 글로벌 심포지엄 개최 및 파텔 교수 멘토링. 빅 이벤트 기반 높은 기대감 형성.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신약', '임상', '항암']</t>
+          <t>['항암신약', '심포지엄', '바이오']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.36</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="H13" t="n">
         <v>2.08</v>
@@ -1622,7 +1622,7 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>15100738224</v>
+        <v>15464645794</v>
       </c>
       <c r="P13" t="n">
         <v>4795</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88200</v>
+        <v>88100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G14" t="n">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="H14" t="n">
         <v>23.56</v>
@@ -1714,7 +1714,7 @@
         <v>23.59</v>
       </c>
       <c r="O14" t="n">
-        <v>148577809950</v>
+        <v>151740238400</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>252000</v>
+        <v>251750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="G15" t="n">
-        <v>1715</v>
+        <v>1738</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>2365784350250</v>
+        <v>2458200887750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 언급 위주로, 실제 사업이나 실적에 대한 구체적인 팩트 기반 분석은 부족한 상황.</t>
+          <t>대통령 선거 결과에 따른 주가 전망 언급. 정치적 이슈가 주가에 영향을 미칠 것이라는 기대감과 부정적 전망이 혼재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치', '투자', '전망']</t>
+          <t>['대통령', '선거', '주가전망']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11810</v>
+        <v>11780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-4.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.72</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
         <v>69</v>
@@ -1892,13 +1892,13 @@
         <v>13230</v>
       </c>
       <c r="M16" t="n">
-        <v>11760</v>
+        <v>11750</v>
       </c>
       <c r="N16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>55443838975</v>
+        <v>55682560205</v>
       </c>
       <c r="P16" t="n">
         <v>20850</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18870</v>
+        <v>18910</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.13%</t>
+          <t>-4.93%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H17" t="n">
         <v>10.55</v>
@@ -1990,7 +1990,7 @@
         <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>55770216885</v>
+        <v>56637006030</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1718000</v>
+        <v>1721000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="G18" t="n">
-        <v>1340</v>
+        <v>1512</v>
       </c>
       <c r="H18" t="n">
         <v>50.47</v>
@@ -2082,7 +2082,7 @@
         <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3982490875500</v>
+        <v>4052808092000</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금리 인상 불확실성 해소 기대감과 함께 주가 하락에 대한 우려가 혼재. 투자자들의 심리적 동요가 큰 상태.</t>
+          <t>금리 인상 불확실성 해소 기대 속 하락세 지속. 정치적 이슈와 반도체 투자 시점에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['금리', '주가', '심리']</t>
+          <t>['금리인상', '반도체', '하락세']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13870</v>
+        <v>13810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.71%</t>
+          <t>-6.12%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>26679955930</v>
+        <v>27248232340</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11540</v>
+        <v>11420</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.31%</t>
+          <t>-8.27%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.51</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H20" t="n">
         <v>17.58</v>
@@ -2260,13 +2260,13 @@
         <v>13900</v>
       </c>
       <c r="M20" t="n">
-        <v>11430</v>
+        <v>11310</v>
       </c>
       <c r="N20" t="n">
         <v>17.07</v>
       </c>
       <c r="O20" t="n">
-        <v>59858135050</v>
+        <v>61058760110</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외인 매수세 유입과 거래량 증가에 따른 단기 급등 기대감, 그러나 투자 주의 및 외인 매도 전환 가능성 언급.</t>
+          <t>외인 매수세 유입 속 급등주 기대감. 단기 거래량 증가 및 수급 논의.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['수급', '거래량', '단기']</t>
+          <t>['외인매수', '급등주', '수급']</t>
         </is>
       </c>
       <c r="X20" t="n">
